--- a/BOM/Fob_Transmitter/JLCPCB-BOM.xlsx
+++ b/BOM/Fob_Transmitter/JLCPCB-BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>Comment</t>
   </si>
@@ -151,6 +151,15 @@
   </si>
   <si>
     <t>LCSC Part Number</t>
+  </si>
+  <si>
+    <t>DL-TX1A-433M</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>C381208</t>
   </si>
 </sst>
 </file>
@@ -200,7 +209,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -282,11 +291,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -307,6 +349,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -596,7 +647,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -773,6 +824,20 @@
         <v>42</v>
       </c>
     </row>
+    <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BOM/Fob_Transmitter/JLCPCB-BOM.xlsx
+++ b/BOM/Fob_Transmitter/JLCPCB-BOM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\OliverStanton-WaterMonitor\BOM\Fob_Transmitter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\OliverStanton-WaterMonitor\BOM\Fob_Transmitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -126,9 +126,6 @@
     <t>C14664</t>
   </si>
   <si>
-    <t>C2718488</t>
-  </si>
-  <si>
     <t>C492404</t>
   </si>
   <si>
@@ -160,12 +157,15 @@
   </si>
   <si>
     <t>C381208</t>
+  </si>
+  <si>
+    <t>C2897366</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -667,7 +667,7 @@
         <v>23</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -723,7 +723,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -737,7 +737,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -751,7 +751,7 @@
         <v>27</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -765,7 +765,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -779,7 +779,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -793,7 +793,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -807,7 +807,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -821,21 +821,21 @@
         <v>31</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/BOM/Fob_Transmitter/JLCPCB-BOM.xlsx
+++ b/BOM/Fob_Transmitter/JLCPCB-BOM.xlsx
@@ -126,9 +126,6 @@
     <t>C14664</t>
   </si>
   <si>
-    <t>C2718488</t>
-  </si>
-  <si>
     <t>C492404</t>
   </si>
   <si>
@@ -160,6 +157,9 @@
   </si>
   <si>
     <t>C381208</t>
+  </si>
+  <si>
+    <t>C358717</t>
   </si>
 </sst>
 </file>
@@ -328,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -359,6 +359,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -667,7 +670,7 @@
         <v>23</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -722,8 +725,8 @@
       <c r="C5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>35</v>
+      <c r="D5" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -737,7 +740,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -751,7 +754,7 @@
         <v>27</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -765,7 +768,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -779,7 +782,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -793,7 +796,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -807,7 +810,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -821,21 +824,21 @@
         <v>31</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
